--- a/tests/testthat/testCases/Test_data_sansComments.xlsx
+++ b/tests/testthat/testCases/Test_data_sansComments.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/aalamshahi/Packages/PETConnector/tests/testthat/testCases/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CF836510-F175-364A-9719-E29DF1B09BE4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ED90635A-ADE3-4844-B7D3-13CA2A0F905C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="800" yWindow="760" windowWidth="33760" windowHeight="20000" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3860" yWindow="760" windowWidth="41180" windowHeight="20000" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="person" sheetId="1" r:id="rId1"/>
@@ -627,7 +627,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:K29"/>
+  <dimension ref="A1:K28"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="2" max="4" width="35.5" customWidth="1"/>
@@ -1118,8 +1118,41 @@
         <v>0</v>
       </c>
     </row>
+    <row r="22" spans="1:11" ht="16" x14ac:dyDescent="0.2">
+      <c r="A22" s="1">
+        <v>102</v>
+      </c>
+      <c r="B22" s="1">
+        <v>8532</v>
+      </c>
+      <c r="C22" s="1">
+        <v>1</v>
+      </c>
+      <c r="D22" s="1">
+        <v>6</v>
+      </c>
+      <c r="E22" s="1">
+        <v>2000</v>
+      </c>
+      <c r="F22" s="1">
+        <v>0</v>
+      </c>
+      <c r="G22" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="1:11" ht="16" x14ac:dyDescent="0.2">
+      <c r="F23" s="1"/>
+    </row>
     <row r="24" spans="1:11" ht="16" x14ac:dyDescent="0.2">
+      <c r="A24" s="1"/>
+      <c r="B24" s="1"/>
+      <c r="C24" s="1"/>
+      <c r="E24" s="1"/>
       <c r="F24" s="1"/>
+      <c r="G24" s="1"/>
+      <c r="H24" s="4"/>
+      <c r="K24" s="4"/>
     </row>
     <row r="25" spans="1:11" ht="16" x14ac:dyDescent="0.2">
       <c r="A25" s="1"/>
@@ -1148,8 +1181,6 @@
       <c r="E27" s="1"/>
       <c r="F27" s="1"/>
       <c r="G27" s="1"/>
-      <c r="H27" s="4"/>
-      <c r="K27" s="4"/>
     </row>
     <row r="28" spans="1:11" ht="16" x14ac:dyDescent="0.2">
       <c r="A28" s="1"/>
@@ -1159,14 +1190,6 @@
       <c r="F28" s="1"/>
       <c r="G28" s="1"/>
     </row>
-    <row r="29" spans="1:11" ht="16" x14ac:dyDescent="0.2">
-      <c r="A29" s="1"/>
-      <c r="B29" s="1"/>
-      <c r="C29" s="1"/>
-      <c r="E29" s="1"/>
-      <c r="F29" s="1"/>
-      <c r="G29" s="1"/>
-    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -1174,7 +1197,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BB104438-4099-6E40-90B1-739F61573A13}">
-  <dimension ref="A1:J17"/>
+  <dimension ref="A1:J19"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11.5" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="2" max="2" width="18.6640625" customWidth="1"/>
@@ -1691,6 +1714,64 @@
       </c>
       <c r="J17" s="1"/>
     </row>
+    <row r="18" spans="1:10" ht="16" x14ac:dyDescent="0.2">
+      <c r="A18" s="1">
+        <v>102</v>
+      </c>
+      <c r="B18" s="1">
+        <v>71</v>
+      </c>
+      <c r="C18" s="10">
+        <v>44296</v>
+      </c>
+      <c r="D18" s="10">
+        <v>44568</v>
+      </c>
+      <c r="E18" s="1">
+        <v>270</v>
+      </c>
+      <c r="F18" s="1">
+        <v>4092289</v>
+      </c>
+      <c r="G18" s="1">
+        <v>4015701</v>
+      </c>
+      <c r="H18" s="1">
+        <v>4188540</v>
+      </c>
+      <c r="I18" s="1">
+        <v>4188539</v>
+      </c>
+    </row>
+    <row r="19" spans="1:10" ht="16" x14ac:dyDescent="0.2">
+      <c r="A19" s="1">
+        <v>102</v>
+      </c>
+      <c r="B19" s="1">
+        <v>72</v>
+      </c>
+      <c r="C19" s="10">
+        <v>44296</v>
+      </c>
+      <c r="D19" s="10">
+        <v>44568</v>
+      </c>
+      <c r="E19" s="1">
+        <v>270</v>
+      </c>
+      <c r="F19" s="1">
+        <v>4092289</v>
+      </c>
+      <c r="G19" s="1">
+        <v>4015701</v>
+      </c>
+      <c r="H19" s="1">
+        <v>4188540</v>
+      </c>
+      <c r="I19" s="1">
+        <v>4188539</v>
+      </c>
+    </row>
   </sheetData>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:I17">
     <sortCondition ref="G1:G17"/>
@@ -1701,7 +1782,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E2B8B433-8712-6348-9439-118BA945D9FC}">
-  <dimension ref="A1:E21"/>
+  <dimension ref="A1:E22"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11.5" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="22.1640625" bestFit="1" customWidth="1"/>
@@ -2067,6 +2148,23 @@
         <v>32880</v>
       </c>
     </row>
+    <row r="22" spans="1:5" ht="16" x14ac:dyDescent="0.2">
+      <c r="A22" s="1">
+        <v>102</v>
+      </c>
+      <c r="B22" s="1">
+        <v>102</v>
+      </c>
+      <c r="C22" s="6">
+        <v>38718</v>
+      </c>
+      <c r="D22" s="6">
+        <v>45657</v>
+      </c>
+      <c r="E22" s="1">
+        <v>32880</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -2074,7 +2172,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EED5A0E5-6553-46ED-AC90-012DDE271310}">
-  <dimension ref="A1:F18"/>
+  <dimension ref="A1:F20"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="3" max="3" width="18.1640625" bestFit="1" customWidth="1"/>
@@ -2441,6 +2539,46 @@
       </c>
       <c r="F18" s="11">
         <v>32830</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" ht="17" x14ac:dyDescent="0.2">
+      <c r="A19" s="4">
+        <v>18</v>
+      </c>
+      <c r="B19" s="4">
+        <v>102</v>
+      </c>
+      <c r="C19" s="11">
+        <v>4145947</v>
+      </c>
+      <c r="D19" s="12">
+        <v>44743</v>
+      </c>
+      <c r="E19" s="12">
+        <v>44743</v>
+      </c>
+      <c r="F19" s="11">
+        <v>32820</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6" ht="17" x14ac:dyDescent="0.2">
+      <c r="A20" s="4">
+        <v>19</v>
+      </c>
+      <c r="B20" s="4">
+        <v>103</v>
+      </c>
+      <c r="C20" s="11">
+        <v>4145947</v>
+      </c>
+      <c r="D20" s="12">
+        <v>44744</v>
+      </c>
+      <c r="E20" s="12">
+        <v>44806</v>
+      </c>
+      <c r="F20" s="11">
+        <v>32821</v>
       </c>
     </row>
   </sheetData>
@@ -3366,7 +3504,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A5BBCCA6-1E90-4542-A320-9B59DFDDE9AE}">
-  <dimension ref="A1:K10"/>
+  <dimension ref="A1:K12"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11.5" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="13.5" customWidth="1"/>
@@ -3619,12 +3757,83 @@
         <v>7</v>
       </c>
     </row>
+    <row r="11" spans="1:11" ht="16" x14ac:dyDescent="0.2">
+      <c r="A11" s="1">
+        <v>72</v>
+      </c>
+      <c r="B11" s="1">
+        <v>17</v>
+      </c>
+      <c r="C11" s="1">
+        <v>17</v>
+      </c>
+      <c r="D11">
+        <v>4092289</v>
+      </c>
+      <c r="E11" s="1">
+        <v>4000</v>
+      </c>
+      <c r="F11" s="1">
+        <v>4188540</v>
+      </c>
+      <c r="G11" s="1">
+        <v>4188540</v>
+      </c>
+      <c r="H11" s="1">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="12" spans="1:11" ht="16" x14ac:dyDescent="0.2">
+      <c r="A12" s="1">
+        <v>71</v>
+      </c>
+      <c r="B12" s="1">
+        <v>18</v>
+      </c>
+      <c r="C12" s="1">
+        <v>18</v>
+      </c>
+      <c r="D12">
+        <v>4092289</v>
+      </c>
+      <c r="E12" s="1">
+        <v>4000</v>
+      </c>
+      <c r="F12" s="1">
+        <v>4188540</v>
+      </c>
+      <c r="G12" s="1">
+        <v>4188540</v>
+      </c>
+      <c r="H12" s="1">
+        <v>10</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="2f696df8-7461-455e-9bf1-ef56149775f2">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101005E48E57FAF33F44FB5E762D78C70B43B" ma:contentTypeVersion="9" ma:contentTypeDescription="Een nieuw document maken." ma:contentTypeScope="" ma:versionID="09261b8c9db6496040fa98c128102db7">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="2f696df8-7461-455e-9bf1-ef56149775f2" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="c87049393a058ff896145aa7aaeb09f0" ns2:_="">
     <xsd:import namespace="2f696df8-7461-455e-9bf1-ef56149775f2"/>
@@ -3796,39 +4005,10 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="2f696df8-7461-455e-9bf1-ef56149775f2">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5C331738-2870-4EAF-86B4-6F4811A40645}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{24F405B8-D94E-404D-BACC-4EAF448A1B08}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="2f696df8-7461-455e-9bf1-ef56149775f2"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -3850,9 +4030,19 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{24F405B8-D94E-404D-BACC-4EAF448A1B08}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5C331738-2870-4EAF-86B4-6F4811A40645}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="2f696df8-7461-455e-9bf1-ef56149775f2"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
--- a/tests/testthat/testCases/Test_data_sansComments.xlsx
+++ b/tests/testthat/testCases/Test_data_sansComments.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/aalamshahi/Packages/PETConnector/tests/testthat/testCases/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ED90635A-ADE3-4844-B7D3-13CA2A0F905C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5EB5FB0F-9B92-2D4C-9768-E1F0AA2D99CA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3860" yWindow="760" windowWidth="41180" windowHeight="20000" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="920" windowWidth="34560" windowHeight="20000" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="person" sheetId="1" r:id="rId1"/>
@@ -3504,7 +3504,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A5BBCCA6-1E90-4542-A320-9B59DFDDE9AE}">
-  <dimension ref="A1:K12"/>
+  <dimension ref="A1:K14"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11.5" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="13.5" customWidth="1"/>
@@ -3730,68 +3730,60 @@
       <c r="D9">
         <v>443213</v>
       </c>
+      <c r="E9" s="1"/>
+      <c r="F9" s="1"/>
+      <c r="G9" s="1"/>
+      <c r="H9" s="1"/>
     </row>
     <row r="10" spans="1:11" ht="16" x14ac:dyDescent="0.2">
       <c r="A10" s="1">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B10" s="1">
-        <v>16</v>
+        <v>111</v>
       </c>
       <c r="C10" s="1">
-        <v>16</v>
+        <v>111</v>
       </c>
       <c r="D10">
         <v>443213</v>
       </c>
-      <c r="E10" s="1">
-        <v>3000</v>
-      </c>
-      <c r="F10" s="1">
-        <v>4188539</v>
-      </c>
-      <c r="G10" s="1">
-        <v>4188539</v>
-      </c>
-      <c r="H10" s="1">
-        <v>7</v>
-      </c>
     </row>
     <row r="11" spans="1:11" ht="16" x14ac:dyDescent="0.2">
       <c r="A11" s="1">
-        <v>72</v>
+        <v>9</v>
       </c>
       <c r="B11" s="1">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C11" s="1">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D11">
-        <v>4092289</v>
+        <v>443213</v>
       </c>
       <c r="E11" s="1">
-        <v>4000</v>
+        <v>3000</v>
       </c>
       <c r="F11" s="1">
-        <v>4188540</v>
+        <v>4188539</v>
       </c>
       <c r="G11" s="1">
-        <v>4188540</v>
+        <v>4188539</v>
       </c>
       <c r="H11" s="1">
-        <v>10</v>
+        <v>7</v>
       </c>
     </row>
     <row r="12" spans="1:11" ht="16" x14ac:dyDescent="0.2">
       <c r="A12" s="1">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B12" s="1">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C12" s="1">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D12">
         <v>4092289</v>
@@ -3806,6 +3798,59 @@
         <v>4188540</v>
       </c>
       <c r="H12" s="1">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="13" spans="1:11" ht="16" x14ac:dyDescent="0.2">
+      <c r="A13" s="1">
+        <v>71</v>
+      </c>
+      <c r="B13" s="1">
+        <v>17</v>
+      </c>
+      <c r="C13" s="1">
+        <v>17</v>
+      </c>
+      <c r="D13">
+        <v>4092289</v>
+      </c>
+      <c r="E13" s="1">
+        <v>4000</v>
+      </c>
+      <c r="F13" s="1">
+        <v>4188540</v>
+      </c>
+      <c r="G13" s="1">
+        <v>4188540</v>
+      </c>
+      <c r="H13" s="1">
+        <v>10</v>
+      </c>
+      <c r="I13" s="4"/>
+    </row>
+    <row r="14" spans="1:11" ht="16" x14ac:dyDescent="0.2">
+      <c r="A14" s="1">
+        <v>71</v>
+      </c>
+      <c r="B14" s="1">
+        <v>18</v>
+      </c>
+      <c r="C14" s="1">
+        <v>18</v>
+      </c>
+      <c r="D14">
+        <v>4092289</v>
+      </c>
+      <c r="E14" s="1">
+        <v>4000</v>
+      </c>
+      <c r="F14" s="1">
+        <v>4188540</v>
+      </c>
+      <c r="G14" s="1">
+        <v>4188540</v>
+      </c>
+      <c r="H14" s="1">
         <v>10</v>
       </c>
     </row>
@@ -3815,15 +3860,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
     <lcf76f155ced4ddcb4097134ff3c332f xmlns="2f696df8-7461-455e-9bf1-ef56149775f2">
@@ -3833,7 +3869,7 @@
 </p:properties>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101005E48E57FAF33F44FB5E762D78C70B43B" ma:contentTypeVersion="9" ma:contentTypeDescription="Een nieuw document maken." ma:contentTypeScope="" ma:versionID="09261b8c9db6496040fa98c128102db7">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="2f696df8-7461-455e-9bf1-ef56149775f2" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="c87049393a058ff896145aa7aaeb09f0" ns2:_="">
     <xsd:import namespace="2f696df8-7461-455e-9bf1-ef56149775f2"/>
@@ -4005,15 +4041,16 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{24F405B8-D94E-404D-BACC-4EAF448A1B08}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7DDF05F8-3308-4EA3-8F5D-FC78E20AC719}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
@@ -4029,7 +4066,7 @@
 </ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5C331738-2870-4EAF-86B4-6F4811A40645}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -4045,4 +4082,12 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{24F405B8-D94E-404D-BACC-4EAF448A1B08}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
--- a/tests/testthat/testCases/Test_data_sansComments.xlsx
+++ b/tests/testthat/testCases/Test_data_sansComments.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/aalamshahi/Packages/PETConnector/tests/testthat/testCases/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ED90635A-ADE3-4844-B7D3-13CA2A0F905C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{27DD172C-0CBC-5C40-B209-3DD87432601E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3860" yWindow="760" windowWidth="41180" windowHeight="20000" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="920" windowWidth="34560" windowHeight="20000" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="person" sheetId="1" r:id="rId1"/>
@@ -2588,7 +2588,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7613E543-FC05-4844-9753-12567E4D8F20}">
-  <dimension ref="A1:F45"/>
+  <dimension ref="A1:F47"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11.5" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="26" style="2" customWidth="1"/>
@@ -2943,7 +2943,7 @@
         <v>1147314</v>
       </c>
       <c r="B21">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C21" s="3">
         <v>1147314</v>
@@ -2960,13 +2960,13 @@
         <v>1147314</v>
       </c>
       <c r="B22">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C22" s="3">
         <v>1147314</v>
       </c>
       <c r="D22">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="E22">
         <v>40485452</v>
@@ -2977,47 +2977,47 @@
         <v>1147314</v>
       </c>
       <c r="B23">
+        <v>14</v>
+      </c>
+      <c r="C23" s="3">
+        <v>1147314</v>
+      </c>
+      <c r="D23">
         <v>15</v>
       </c>
-      <c r="C23" s="3">
-        <v>1147314</v>
-      </c>
-      <c r="D23">
+      <c r="E23">
+        <v>40485452</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A24" s="3">
+        <v>1147314</v>
+      </c>
+      <c r="B24">
+        <v>15</v>
+      </c>
+      <c r="C24" s="3">
+        <v>1147314</v>
+      </c>
+      <c r="D24">
         <v>14</v>
       </c>
-      <c r="E23">
+      <c r="E24">
         <v>4285883</v>
       </c>
     </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A24" s="5">
-        <v>1147314</v>
-      </c>
-      <c r="B24" s="4">
-        <v>1</v>
-      </c>
-      <c r="C24" s="5">
-        <v>1147314</v>
-      </c>
-      <c r="D24" s="4">
+    <row r="25" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A25" s="5">
+        <v>1147314</v>
+      </c>
+      <c r="B25" s="4">
+        <v>1</v>
+      </c>
+      <c r="C25" s="5">
+        <v>1147314</v>
+      </c>
+      <c r="D25" s="4">
         <v>3</v>
-      </c>
-      <c r="E24">
-        <v>4326600</v>
-      </c>
-    </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A25" s="3">
-        <v>1147314</v>
-      </c>
-      <c r="B25">
-        <v>1</v>
-      </c>
-      <c r="C25" s="3">
-        <v>1147314</v>
-      </c>
-      <c r="D25">
-        <v>4</v>
       </c>
       <c r="E25">
         <v>4326600</v>
@@ -3034,7 +3034,7 @@
         <v>1147314</v>
       </c>
       <c r="D26">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E26">
         <v>4326600</v>
@@ -3045,13 +3045,13 @@
         <v>1147314</v>
       </c>
       <c r="B27">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C27" s="3">
         <v>1147314</v>
       </c>
       <c r="D27">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E27">
         <v>4326600</v>
@@ -3068,7 +3068,7 @@
         <v>1147314</v>
       </c>
       <c r="D28">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E28">
         <v>4326600</v>
@@ -3085,7 +3085,7 @@
         <v>1147314</v>
       </c>
       <c r="D29">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E29">
         <v>4326600</v>
@@ -3096,13 +3096,13 @@
         <v>1147314</v>
       </c>
       <c r="B30">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C30" s="3">
         <v>1147314</v>
       </c>
       <c r="D30">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E30">
         <v>4326600</v>
@@ -3119,7 +3119,7 @@
         <v>1147314</v>
       </c>
       <c r="D31">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E31">
         <v>4326600</v>
@@ -3130,13 +3130,13 @@
         <v>1147314</v>
       </c>
       <c r="B32">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C32" s="3">
         <v>1147314</v>
       </c>
       <c r="D32">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E32">
         <v>4326600</v>
@@ -3153,7 +3153,7 @@
         <v>1147314</v>
       </c>
       <c r="D33">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E33">
         <v>4326600</v>
@@ -3164,13 +3164,13 @@
         <v>1147314</v>
       </c>
       <c r="B34">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C34" s="3">
         <v>1147314</v>
       </c>
       <c r="D34">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E34">
         <v>4326600</v>
@@ -3187,7 +3187,7 @@
         <v>1147314</v>
       </c>
       <c r="D35">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E35">
         <v>4326600</v>
@@ -3198,13 +3198,13 @@
         <v>1147314</v>
       </c>
       <c r="B36">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C36" s="3">
         <v>1147314</v>
       </c>
       <c r="D36">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="E36">
         <v>4326600</v>
@@ -3221,7 +3221,7 @@
         <v>1147314</v>
       </c>
       <c r="D37">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E37">
         <v>4326600</v>
@@ -3232,13 +3232,13 @@
         <v>1147314</v>
       </c>
       <c r="B38">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C38" s="3">
         <v>1147314</v>
       </c>
       <c r="D38">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E38">
         <v>4326600</v>
@@ -3249,7 +3249,7 @@
         <v>1147314</v>
       </c>
       <c r="B39">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C39" s="3">
         <v>1147314</v>
@@ -3266,13 +3266,13 @@
         <v>1147314</v>
       </c>
       <c r="B40">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="C40" s="3">
         <v>1147314</v>
       </c>
       <c r="D40">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="E40">
         <v>4326600</v>
@@ -3289,7 +3289,7 @@
         <v>1147314</v>
       </c>
       <c r="D41">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E41">
         <v>4326600</v>
@@ -3300,13 +3300,13 @@
         <v>1147314</v>
       </c>
       <c r="B42">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C42" s="3">
         <v>1147314</v>
       </c>
       <c r="D42">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="E42">
         <v>4326600</v>
@@ -3317,7 +3317,7 @@
         <v>1147314</v>
       </c>
       <c r="B43">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C43" s="3">
         <v>1147314</v>
@@ -3334,13 +3334,13 @@
         <v>1147314</v>
       </c>
       <c r="B44">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C44" s="3">
         <v>1147314</v>
       </c>
       <c r="D44">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="E44">
         <v>4326600</v>
@@ -3351,17 +3351,38 @@
         <v>1147314</v>
       </c>
       <c r="B45">
+        <v>14</v>
+      </c>
+      <c r="C45" s="3">
+        <v>1147314</v>
+      </c>
+      <c r="D45">
         <v>15</v>
-      </c>
-      <c r="C45" s="3">
-        <v>1147314</v>
-      </c>
-      <c r="D45">
-        <v>14</v>
       </c>
       <c r="E45">
         <v>4326600</v>
       </c>
+    </row>
+    <row r="46" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A46" s="3">
+        <v>1147314</v>
+      </c>
+      <c r="B46">
+        <v>15</v>
+      </c>
+      <c r="C46" s="3">
+        <v>1147314</v>
+      </c>
+      <c r="D46">
+        <v>14</v>
+      </c>
+      <c r="E46">
+        <v>4326600</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A47" s="3"/>
+      <c r="C47" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -3504,7 +3525,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A5BBCCA6-1E90-4542-A320-9B59DFDDE9AE}">
-  <dimension ref="A1:K12"/>
+  <dimension ref="A1:K14"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11.5" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="13.5" customWidth="1"/>
@@ -3730,68 +3751,60 @@
       <c r="D9">
         <v>443213</v>
       </c>
+      <c r="E9" s="1"/>
+      <c r="F9" s="1"/>
+      <c r="G9" s="1"/>
+      <c r="H9" s="1"/>
     </row>
     <row r="10" spans="1:11" ht="16" x14ac:dyDescent="0.2">
       <c r="A10" s="1">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B10" s="1">
-        <v>16</v>
+        <v>111</v>
       </c>
       <c r="C10" s="1">
-        <v>16</v>
+        <v>111</v>
       </c>
       <c r="D10">
         <v>443213</v>
       </c>
-      <c r="E10" s="1">
-        <v>3000</v>
-      </c>
-      <c r="F10" s="1">
-        <v>4188539</v>
-      </c>
-      <c r="G10" s="1">
-        <v>4188539</v>
-      </c>
-      <c r="H10" s="1">
-        <v>7</v>
-      </c>
     </row>
     <row r="11" spans="1:11" ht="16" x14ac:dyDescent="0.2">
       <c r="A11" s="1">
-        <v>72</v>
+        <v>9</v>
       </c>
       <c r="B11" s="1">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C11" s="1">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D11">
-        <v>4092289</v>
+        <v>443213</v>
       </c>
       <c r="E11" s="1">
-        <v>4000</v>
+        <v>3000</v>
       </c>
       <c r="F11" s="1">
-        <v>4188540</v>
+        <v>4188539</v>
       </c>
       <c r="G11" s="1">
-        <v>4188540</v>
+        <v>4188539</v>
       </c>
       <c r="H11" s="1">
-        <v>10</v>
+        <v>7</v>
       </c>
     </row>
     <row r="12" spans="1:11" ht="16" x14ac:dyDescent="0.2">
       <c r="A12" s="1">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B12" s="1">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C12" s="1">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D12">
         <v>4092289</v>
@@ -3806,6 +3819,59 @@
         <v>4188540</v>
       </c>
       <c r="H12" s="1">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="13" spans="1:11" ht="16" x14ac:dyDescent="0.2">
+      <c r="A13" s="1">
+        <v>71</v>
+      </c>
+      <c r="B13" s="1">
+        <v>17</v>
+      </c>
+      <c r="C13" s="1">
+        <v>17</v>
+      </c>
+      <c r="D13">
+        <v>4092289</v>
+      </c>
+      <c r="E13" s="1">
+        <v>4000</v>
+      </c>
+      <c r="F13" s="1">
+        <v>4188540</v>
+      </c>
+      <c r="G13" s="1">
+        <v>4188540</v>
+      </c>
+      <c r="H13" s="1">
+        <v>10</v>
+      </c>
+      <c r="I13" s="4"/>
+    </row>
+    <row r="14" spans="1:11" ht="16" x14ac:dyDescent="0.2">
+      <c r="A14" s="1">
+        <v>71</v>
+      </c>
+      <c r="B14" s="1">
+        <v>18</v>
+      </c>
+      <c r="C14" s="1">
+        <v>18</v>
+      </c>
+      <c r="D14">
+        <v>4092289</v>
+      </c>
+      <c r="E14" s="1">
+        <v>4000</v>
+      </c>
+      <c r="F14" s="1">
+        <v>4188540</v>
+      </c>
+      <c r="G14" s="1">
+        <v>4188540</v>
+      </c>
+      <c r="H14" s="1">
         <v>10</v>
       </c>
     </row>
@@ -3815,15 +3881,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
     <lcf76f155ced4ddcb4097134ff3c332f xmlns="2f696df8-7461-455e-9bf1-ef56149775f2">
@@ -3833,7 +3890,7 @@
 </p:properties>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101005E48E57FAF33F44FB5E762D78C70B43B" ma:contentTypeVersion="9" ma:contentTypeDescription="Een nieuw document maken." ma:contentTypeScope="" ma:versionID="09261b8c9db6496040fa98c128102db7">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="2f696df8-7461-455e-9bf1-ef56149775f2" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="c87049393a058ff896145aa7aaeb09f0" ns2:_="">
     <xsd:import namespace="2f696df8-7461-455e-9bf1-ef56149775f2"/>
@@ -4005,15 +4062,16 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{24F405B8-D94E-404D-BACC-4EAF448A1B08}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7DDF05F8-3308-4EA3-8F5D-FC78E20AC719}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
@@ -4029,7 +4087,7 @@
 </ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5C331738-2870-4EAF-86B4-6F4811A40645}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -4045,4 +4103,12 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{24F405B8-D94E-404D-BACC-4EAF448A1B08}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
--- a/tests/testthat/testCases/Test_data_sansComments.xlsx
+++ b/tests/testthat/testCases/Test_data_sansComments.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/aalamshahi/Packages/PETConnector/tests/testthat/testCases/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{27DD172C-0CBC-5C40-B209-3DD87432601E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2A65C81F-CE00-6245-AC4C-27807CF202EB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="920" windowWidth="34560" windowHeight="20000" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="14960" yWindow="980" windowWidth="34560" windowHeight="20000" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="person" sheetId="1" r:id="rId1"/>
@@ -1782,7 +1782,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E2B8B433-8712-6348-9439-118BA945D9FC}">
-  <dimension ref="A1:E22"/>
+  <dimension ref="A1:E23"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11.5" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="22.1640625" bestFit="1" customWidth="1"/>
@@ -2023,7 +2023,7 @@
         <v>44568</v>
       </c>
       <c r="D14" s="6">
-        <v>45657</v>
+        <v>45656</v>
       </c>
       <c r="E14" s="1">
         <v>32880</v>
@@ -2031,13 +2031,13 @@
     </row>
     <row r="15" spans="1:5" ht="16" x14ac:dyDescent="0.2">
       <c r="A15" s="1">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B15" s="1">
-        <v>14</v>
-      </c>
-      <c r="C15" s="6">
-        <v>38718</v>
+        <v>13</v>
+      </c>
+      <c r="C15" s="7">
+        <v>44568</v>
       </c>
       <c r="D15" s="6">
         <v>45657</v>
@@ -2048,13 +2048,13 @@
     </row>
     <row r="16" spans="1:5" ht="16" x14ac:dyDescent="0.2">
       <c r="A16" s="1">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B16" s="1">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C16" s="6">
-        <v>44567</v>
+        <v>38718</v>
       </c>
       <c r="D16" s="6">
         <v>45657</v>
@@ -2065,13 +2065,13 @@
     </row>
     <row r="17" spans="1:5" ht="16" x14ac:dyDescent="0.2">
       <c r="A17" s="1">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B17" s="1">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C17" s="6">
-        <v>38718</v>
+        <v>44567</v>
       </c>
       <c r="D17" s="6">
         <v>45657</v>
@@ -2082,10 +2082,10 @@
     </row>
     <row r="18" spans="1:5" ht="16" x14ac:dyDescent="0.2">
       <c r="A18" s="1">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B18" s="1">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C18" s="6">
         <v>38718</v>
@@ -2099,10 +2099,10 @@
     </row>
     <row r="19" spans="1:5" ht="16" x14ac:dyDescent="0.2">
       <c r="A19" s="1">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B19" s="1">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C19" s="6">
         <v>38718</v>
@@ -2116,10 +2116,10 @@
     </row>
     <row r="20" spans="1:5" ht="16" x14ac:dyDescent="0.2">
       <c r="A20" s="1">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B20" s="1">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C20" s="6">
         <v>38718</v>
@@ -2133,10 +2133,10 @@
     </row>
     <row r="21" spans="1:5" ht="16" x14ac:dyDescent="0.2">
       <c r="A21" s="1">
-        <v>100</v>
+        <v>19</v>
       </c>
       <c r="B21" s="1">
-        <v>100</v>
+        <v>19</v>
       </c>
       <c r="C21" s="6">
         <v>38718</v>
@@ -2150,10 +2150,10 @@
     </row>
     <row r="22" spans="1:5" ht="16" x14ac:dyDescent="0.2">
       <c r="A22" s="1">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="B22" s="1">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="C22" s="6">
         <v>38718</v>
@@ -2162,6 +2162,23 @@
         <v>45657</v>
       </c>
       <c r="E22" s="1">
+        <v>32880</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" ht="16" x14ac:dyDescent="0.2">
+      <c r="A23" s="1">
+        <v>102</v>
+      </c>
+      <c r="B23" s="1">
+        <v>102</v>
+      </c>
+      <c r="C23" s="6">
+        <v>38718</v>
+      </c>
+      <c r="D23" s="6">
+        <v>45657</v>
+      </c>
+      <c r="E23" s="1">
         <v>32880</v>
       </c>
     </row>
@@ -3881,13 +3898,12 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="2f696df8-7461-455e-9bf1-ef56149775f2">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -4063,26 +4079,19 @@
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="2f696df8-7461-455e-9bf1-ef56149775f2">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7DDF05F8-3308-4EA3-8F5D-FC78E20AC719}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{24F405B8-D94E-404D-BACC-4EAF448A1B08}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="2f696df8-7461-455e-9bf1-ef56149775f2"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -4106,9 +4115,17 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{24F405B8-D94E-404D-BACC-4EAF448A1B08}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7DDF05F8-3308-4EA3-8F5D-FC78E20AC719}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="2f696df8-7461-455e-9bf1-ef56149775f2"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
--- a/tests/testthat/testCases/Test_data_sansComments.xlsx
+++ b/tests/testthat/testCases/Test_data_sansComments.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/aalamshahi/Packages/PETConnector/tests/testthat/testCases/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2A65C81F-CE00-6245-AC4C-27807CF202EB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C35ED3AC-87FC-964A-812B-415B81FFE2EF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="14960" yWindow="980" windowWidth="34560" windowHeight="20000" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="980" windowWidth="34560" windowHeight="20000" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="person" sheetId="1" r:id="rId1"/>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="55">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="62" uniqueCount="57">
   <si>
     <t>person_id</t>
   </si>
@@ -207,6 +207,12 @@
   </si>
   <si>
     <t>pregnancy_outcome</t>
+  </si>
+  <si>
+    <t>Family 6- Infant of Mother</t>
+  </si>
+  <si>
+    <t>Family 6 - daughter</t>
   </si>
 </sst>
 </file>
@@ -1142,7 +1148,30 @@
       </c>
     </row>
     <row r="23" spans="1:11" ht="16" x14ac:dyDescent="0.2">
-      <c r="F23" s="1"/>
+      <c r="A23" s="1">
+        <v>25</v>
+      </c>
+      <c r="B23" s="1">
+        <v>8532</v>
+      </c>
+      <c r="C23" s="1">
+        <v>1</v>
+      </c>
+      <c r="D23" s="1">
+        <v>7</v>
+      </c>
+      <c r="E23" s="1">
+        <v>2022</v>
+      </c>
+      <c r="F23" s="1">
+        <v>0</v>
+      </c>
+      <c r="G23" s="1">
+        <v>0</v>
+      </c>
+      <c r="H23" t="s">
+        <v>56</v>
+      </c>
     </row>
     <row r="24" spans="1:11" ht="16" x14ac:dyDescent="0.2">
       <c r="A24" s="1"/>
@@ -1782,7 +1811,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E2B8B433-8712-6348-9439-118BA945D9FC}">
-  <dimension ref="A1:E23"/>
+  <dimension ref="A1:E24"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11.5" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="22.1640625" bestFit="1" customWidth="1"/>
@@ -2179,6 +2208,23 @@
         <v>45657</v>
       </c>
       <c r="E23" s="1">
+        <v>32880</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5" ht="16" x14ac:dyDescent="0.2">
+      <c r="A24" s="1">
+        <v>25</v>
+      </c>
+      <c r="B24" s="1">
+        <v>25</v>
+      </c>
+      <c r="C24" s="7">
+        <v>44568</v>
+      </c>
+      <c r="D24" s="8">
+        <v>45657</v>
+      </c>
+      <c r="E24" s="1">
         <v>32880</v>
       </c>
     </row>
@@ -3159,7 +3205,7 @@
         <v>4326600</v>
       </c>
     </row>
-    <row r="33" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A33" s="3">
         <v>1147314</v>
       </c>
@@ -3176,7 +3222,7 @@
         <v>4326600</v>
       </c>
     </row>
-    <row r="34" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A34" s="3">
         <v>1147314</v>
       </c>
@@ -3193,7 +3239,7 @@
         <v>4326600</v>
       </c>
     </row>
-    <row r="35" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A35" s="3">
         <v>1147314</v>
       </c>
@@ -3210,7 +3256,7 @@
         <v>4326600</v>
       </c>
     </row>
-    <row r="36" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A36" s="3">
         <v>1147314</v>
       </c>
@@ -3227,7 +3273,7 @@
         <v>4326600</v>
       </c>
     </row>
-    <row r="37" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A37" s="3">
         <v>1147314</v>
       </c>
@@ -3244,7 +3290,7 @@
         <v>4326600</v>
       </c>
     </row>
-    <row r="38" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A38" s="3">
         <v>1147314</v>
       </c>
@@ -3261,7 +3307,7 @@
         <v>4326600</v>
       </c>
     </row>
-    <row r="39" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A39" s="3">
         <v>1147314</v>
       </c>
@@ -3278,7 +3324,7 @@
         <v>4326600</v>
       </c>
     </row>
-    <row r="40" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A40" s="3">
         <v>1147314</v>
       </c>
@@ -3295,7 +3341,7 @@
         <v>4326600</v>
       </c>
     </row>
-    <row r="41" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A41" s="3">
         <v>1147314</v>
       </c>
@@ -3312,7 +3358,7 @@
         <v>4326600</v>
       </c>
     </row>
-    <row r="42" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A42" s="3">
         <v>1147314</v>
       </c>
@@ -3329,7 +3375,7 @@
         <v>4326600</v>
       </c>
     </row>
-    <row r="43" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A43" s="3">
         <v>1147314</v>
       </c>
@@ -3346,7 +3392,7 @@
         <v>4326600</v>
       </c>
     </row>
-    <row r="44" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A44" s="3">
         <v>1147314</v>
       </c>
@@ -3363,7 +3409,7 @@
         <v>4326600</v>
       </c>
     </row>
-    <row r="45" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A45" s="3">
         <v>1147314</v>
       </c>
@@ -3380,7 +3426,7 @@
         <v>4326600</v>
       </c>
     </row>
-    <row r="46" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A46" s="3">
         <v>1147314</v>
       </c>
@@ -3397,9 +3443,25 @@
         <v>4326600</v>
       </c>
     </row>
-    <row r="47" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A47" s="3"/>
-      <c r="C47" s="3"/>
+    <row r="47" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A47" s="3">
+        <v>1147314</v>
+      </c>
+      <c r="B47">
+        <v>25</v>
+      </c>
+      <c r="C47" s="3">
+        <v>1147314</v>
+      </c>
+      <c r="D47">
+        <v>30</v>
+      </c>
+      <c r="E47">
+        <v>40485452</v>
+      </c>
+      <c r="F47" t="s">
+        <v>55</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -3898,12 +3960,13 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="2f696df8-7461-455e-9bf1-ef56149775f2">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -4079,19 +4142,26 @@
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="2f696df8-7461-455e-9bf1-ef56149775f2">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{24F405B8-D94E-404D-BACC-4EAF448A1B08}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7DDF05F8-3308-4EA3-8F5D-FC78E20AC719}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="2f696df8-7461-455e-9bf1-ef56149775f2"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -4115,17 +4185,9 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7DDF05F8-3308-4EA3-8F5D-FC78E20AC719}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{24F405B8-D94E-404D-BACC-4EAF448A1B08}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="2f696df8-7461-455e-9bf1-ef56149775f2"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
--- a/tests/testthat/testCases/Test_data_sansComments.xlsx
+++ b/tests/testthat/testCases/Test_data_sansComments.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/aalamshahi/Packages/PETConnector/tests/testthat/testCases/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C35ED3AC-87FC-964A-812B-415B81FFE2EF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AE630594-B718-5A42-8E44-47897E3FE2E2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="980" windowWidth="34560" windowHeight="20000" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="980" windowWidth="34560" windowHeight="20000" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="person" sheetId="1" r:id="rId1"/>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="62" uniqueCount="57">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="55">
   <si>
     <t>person_id</t>
   </si>
@@ -207,12 +207,6 @@
   </si>
   <si>
     <t>pregnancy_outcome</t>
-  </si>
-  <si>
-    <t>Family 6- Infant of Mother</t>
-  </si>
-  <si>
-    <t>Family 6 - daughter</t>
   </si>
 </sst>
 </file>
@@ -1169,9 +1163,6 @@
       <c r="G23" s="1">
         <v>0</v>
       </c>
-      <c r="H23" t="s">
-        <v>56</v>
-      </c>
     </row>
     <row r="24" spans="1:11" ht="16" x14ac:dyDescent="0.2">
       <c r="A24" s="1"/>
@@ -3205,7 +3196,7 @@
         <v>4326600</v>
       </c>
     </row>
-    <row r="33" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A33" s="3">
         <v>1147314</v>
       </c>
@@ -3222,7 +3213,7 @@
         <v>4326600</v>
       </c>
     </row>
-    <row r="34" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A34" s="3">
         <v>1147314</v>
       </c>
@@ -3239,7 +3230,7 @@
         <v>4326600</v>
       </c>
     </row>
-    <row r="35" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A35" s="3">
         <v>1147314</v>
       </c>
@@ -3256,7 +3247,7 @@
         <v>4326600</v>
       </c>
     </row>
-    <row r="36" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A36" s="3">
         <v>1147314</v>
       </c>
@@ -3273,7 +3264,7 @@
         <v>4326600</v>
       </c>
     </row>
-    <row r="37" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A37" s="3">
         <v>1147314</v>
       </c>
@@ -3290,7 +3281,7 @@
         <v>4326600</v>
       </c>
     </row>
-    <row r="38" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A38" s="3">
         <v>1147314</v>
       </c>
@@ -3307,7 +3298,7 @@
         <v>4326600</v>
       </c>
     </row>
-    <row r="39" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A39" s="3">
         <v>1147314</v>
       </c>
@@ -3324,7 +3315,7 @@
         <v>4326600</v>
       </c>
     </row>
-    <row r="40" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A40" s="3">
         <v>1147314</v>
       </c>
@@ -3341,7 +3332,7 @@
         <v>4326600</v>
       </c>
     </row>
-    <row r="41" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A41" s="3">
         <v>1147314</v>
       </c>
@@ -3358,7 +3349,7 @@
         <v>4326600</v>
       </c>
     </row>
-    <row r="42" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A42" s="3">
         <v>1147314</v>
       </c>
@@ -3375,7 +3366,7 @@
         <v>4326600</v>
       </c>
     </row>
-    <row r="43" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A43" s="3">
         <v>1147314</v>
       </c>
@@ -3392,7 +3383,7 @@
         <v>4326600</v>
       </c>
     </row>
-    <row r="44" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A44" s="3">
         <v>1147314</v>
       </c>
@@ -3409,7 +3400,7 @@
         <v>4326600</v>
       </c>
     </row>
-    <row r="45" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A45" s="3">
         <v>1147314</v>
       </c>
@@ -3426,7 +3417,7 @@
         <v>4326600</v>
       </c>
     </row>
-    <row r="46" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A46" s="3">
         <v>1147314</v>
       </c>
@@ -3443,7 +3434,7 @@
         <v>4326600</v>
       </c>
     </row>
-    <row r="47" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A47" s="3">
         <v>1147314</v>
       </c>
@@ -3458,9 +3449,6 @@
       </c>
       <c r="E47">
         <v>40485452</v>
-      </c>
-      <c r="F47" t="s">
-        <v>55</v>
       </c>
     </row>
   </sheetData>
@@ -3960,16 +3948,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="2f696df8-7461-455e-9bf1-ef56149775f2">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101005E48E57FAF33F44FB5E762D78C70B43B" ma:contentTypeVersion="9" ma:contentTypeDescription="Een nieuw document maken." ma:contentTypeScope="" ma:versionID="09261b8c9db6496040fa98c128102db7">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="2f696df8-7461-455e-9bf1-ef56149775f2" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="c87049393a058ff896145aa7aaeb09f0" ns2:_="">
     <xsd:import namespace="2f696df8-7461-455e-9bf1-ef56149775f2"/>
@@ -4141,6 +4119,16 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="2f696df8-7461-455e-9bf1-ef56149775f2">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
+</file>
+
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
@@ -4151,22 +4139,6 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7DDF05F8-3308-4EA3-8F5D-FC78E20AC719}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="2f696df8-7461-455e-9bf1-ef56149775f2"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5C331738-2870-4EAF-86B4-6F4811A40645}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -4184,6 +4156,22 @@
 </ds:datastoreItem>
 </file>
 
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7DDF05F8-3308-4EA3-8F5D-FC78E20AC719}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="2f696df8-7461-455e-9bf1-ef56149775f2"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{24F405B8-D94E-404D-BACC-4EAF448A1B08}">
   <ds:schemaRefs>

--- a/tests/testthat/testCases/Test_data_sansComments.xlsx
+++ b/tests/testthat/testCases/Test_data_sansComments.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="10726"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="10817"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/aalamshahi/Packages/PETConnector/tests/testthat/testCases/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AE630594-B718-5A42-8E44-47897E3FE2E2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{99BC1206-A5CE-4D48-A144-6D59706F09B6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="980" windowWidth="34560" windowHeight="20000" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="6160" yWindow="840" windowWidth="25600" windowHeight="15500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="person" sheetId="1" r:id="rId1"/>
@@ -627,7 +627,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:K28"/>
+  <dimension ref="A1:K27"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="2" max="4" width="35.5" customWidth="1"/>
@@ -1165,12 +1165,27 @@
       </c>
     </row>
     <row r="24" spans="1:11" ht="16" x14ac:dyDescent="0.2">
-      <c r="A24" s="1"/>
-      <c r="B24" s="1"/>
-      <c r="C24" s="1"/>
-      <c r="E24" s="1"/>
-      <c r="F24" s="1"/>
-      <c r="G24" s="1"/>
+      <c r="A24" s="1">
+        <v>104</v>
+      </c>
+      <c r="B24" s="1">
+        <v>8532</v>
+      </c>
+      <c r="C24" s="1">
+        <v>1</v>
+      </c>
+      <c r="D24" s="1">
+        <v>6</v>
+      </c>
+      <c r="E24" s="1">
+        <v>1992</v>
+      </c>
+      <c r="F24" s="1">
+        <v>0</v>
+      </c>
+      <c r="G24" s="1">
+        <v>0</v>
+      </c>
       <c r="H24" s="4"/>
       <c r="K24" s="4"/>
     </row>
@@ -1191,8 +1206,6 @@
       <c r="E26" s="1"/>
       <c r="F26" s="1"/>
       <c r="G26" s="1"/>
-      <c r="H26" s="4"/>
-      <c r="K26" s="4"/>
     </row>
     <row r="27" spans="1:11" ht="16" x14ac:dyDescent="0.2">
       <c r="A27" s="1"/>
@@ -1202,14 +1215,6 @@
       <c r="F27" s="1"/>
       <c r="G27" s="1"/>
     </row>
-    <row r="28" spans="1:11" ht="16" x14ac:dyDescent="0.2">
-      <c r="A28" s="1"/>
-      <c r="B28" s="1"/>
-      <c r="C28" s="1"/>
-      <c r="E28" s="1"/>
-      <c r="F28" s="1"/>
-      <c r="G28" s="1"/>
-    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -1217,7 +1222,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BB104438-4099-6E40-90B1-739F61573A13}">
-  <dimension ref="A1:J19"/>
+  <dimension ref="A1:J21"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11.5" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="2" max="2" width="18.6640625" customWidth="1"/>
@@ -1792,6 +1797,64 @@
         <v>4188539</v>
       </c>
     </row>
+    <row r="20" spans="1:10" ht="16" x14ac:dyDescent="0.2">
+      <c r="A20" s="1">
+        <v>104</v>
+      </c>
+      <c r="B20" s="1">
+        <v>43</v>
+      </c>
+      <c r="C20" s="10">
+        <v>43832</v>
+      </c>
+      <c r="D20" s="10">
+        <v>44089</v>
+      </c>
+      <c r="E20" s="1">
+        <v>270</v>
+      </c>
+      <c r="F20" s="1">
+        <v>4092289</v>
+      </c>
+      <c r="G20" s="1">
+        <v>4015701</v>
+      </c>
+      <c r="H20" s="1">
+        <v>4188540</v>
+      </c>
+      <c r="I20" s="1">
+        <v>4188539</v>
+      </c>
+    </row>
+    <row r="21" spans="1:10" ht="16" x14ac:dyDescent="0.2">
+      <c r="A21" s="1">
+        <v>104</v>
+      </c>
+      <c r="B21" s="1">
+        <v>44</v>
+      </c>
+      <c r="C21" s="10">
+        <v>43840</v>
+      </c>
+      <c r="D21" s="10">
+        <v>44094</v>
+      </c>
+      <c r="E21" s="1">
+        <v>270</v>
+      </c>
+      <c r="F21" s="1">
+        <v>4092289</v>
+      </c>
+      <c r="G21" s="1">
+        <v>4015701</v>
+      </c>
+      <c r="H21" s="1">
+        <v>4188540</v>
+      </c>
+      <c r="I21" s="1">
+        <v>4188539</v>
+      </c>
+    </row>
   </sheetData>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:I17">
     <sortCondition ref="G1:G17"/>
@@ -1802,7 +1865,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E2B8B433-8712-6348-9439-118BA945D9FC}">
-  <dimension ref="A1:E24"/>
+  <dimension ref="A1:E25"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11.5" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="22.1640625" bestFit="1" customWidth="1"/>
@@ -2216,6 +2279,23 @@
         <v>45657</v>
       </c>
       <c r="E24" s="1">
+        <v>32880</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5" ht="16" x14ac:dyDescent="0.2">
+      <c r="A25" s="1">
+        <v>104</v>
+      </c>
+      <c r="B25" s="1">
+        <v>104</v>
+      </c>
+      <c r="C25" s="6">
+        <v>38718</v>
+      </c>
+      <c r="D25" s="6">
+        <v>45657</v>
+      </c>
+      <c r="E25" s="1">
         <v>32880</v>
       </c>
     </row>

--- a/tests/testthat/testCases/Test_data_sansComments.xlsx
+++ b/tests/testthat/testCases/Test_data_sansComments.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/aalamshahi/Packages/PETConnector/tests/testthat/testCases/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{99BC1206-A5CE-4D48-A144-6D59706F09B6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{59E8A64A-B2C6-F949-B5CD-B22724A044A3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="6160" yWindow="840" windowWidth="25600" windowHeight="15500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="6220" yWindow="2020" windowWidth="25600" windowHeight="15500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="person" sheetId="1" r:id="rId1"/>
@@ -1190,22 +1190,52 @@
       <c r="K24" s="4"/>
     </row>
     <row r="25" spans="1:11" ht="16" x14ac:dyDescent="0.2">
-      <c r="A25" s="1"/>
-      <c r="B25" s="1"/>
-      <c r="C25" s="1"/>
-      <c r="E25" s="1"/>
-      <c r="F25" s="1"/>
-      <c r="G25" s="1"/>
+      <c r="A25" s="1">
+        <v>105</v>
+      </c>
+      <c r="B25" s="1">
+        <v>8532</v>
+      </c>
+      <c r="C25" s="1">
+        <v>1</v>
+      </c>
+      <c r="D25" s="1">
+        <v>6</v>
+      </c>
+      <c r="E25" s="1">
+        <v>1992</v>
+      </c>
+      <c r="F25" s="1">
+        <v>0</v>
+      </c>
+      <c r="G25" s="1">
+        <v>0</v>
+      </c>
       <c r="H25" s="4"/>
       <c r="K25" s="4"/>
     </row>
     <row r="26" spans="1:11" ht="16" x14ac:dyDescent="0.2">
-      <c r="A26" s="1"/>
-      <c r="B26" s="1"/>
-      <c r="C26" s="1"/>
-      <c r="E26" s="1"/>
-      <c r="F26" s="1"/>
-      <c r="G26" s="1"/>
+      <c r="A26" s="1">
+        <v>106</v>
+      </c>
+      <c r="B26" s="1">
+        <v>8532</v>
+      </c>
+      <c r="C26" s="1">
+        <v>1</v>
+      </c>
+      <c r="D26" s="1">
+        <v>6</v>
+      </c>
+      <c r="E26" s="1">
+        <v>1992</v>
+      </c>
+      <c r="F26" s="1">
+        <v>0</v>
+      </c>
+      <c r="G26" s="1">
+        <v>0</v>
+      </c>
     </row>
     <row r="27" spans="1:11" ht="16" x14ac:dyDescent="0.2">
       <c r="A27" s="1"/>
@@ -1222,7 +1252,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BB104438-4099-6E40-90B1-739F61573A13}">
-  <dimension ref="A1:J21"/>
+  <dimension ref="A1:J26"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11.5" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="2" max="2" width="18.6640625" customWidth="1"/>
@@ -1855,6 +1885,151 @@
         <v>4188539</v>
       </c>
     </row>
+    <row r="22" spans="1:10" ht="16" x14ac:dyDescent="0.2">
+      <c r="A22" s="1">
+        <v>105</v>
+      </c>
+      <c r="B22" s="1">
+        <v>45</v>
+      </c>
+      <c r="C22" s="10">
+        <v>43840</v>
+      </c>
+      <c r="D22" s="10">
+        <v>44094</v>
+      </c>
+      <c r="E22" s="1">
+        <v>270</v>
+      </c>
+      <c r="F22" s="1">
+        <v>4092289</v>
+      </c>
+      <c r="G22" s="1">
+        <v>4015701</v>
+      </c>
+      <c r="H22" s="1">
+        <v>4188540</v>
+      </c>
+      <c r="I22" s="1">
+        <v>4188539</v>
+      </c>
+    </row>
+    <row r="23" spans="1:10" ht="16" x14ac:dyDescent="0.2">
+      <c r="A23" s="1">
+        <v>105</v>
+      </c>
+      <c r="B23" s="1">
+        <v>45</v>
+      </c>
+      <c r="C23" s="10">
+        <v>43832</v>
+      </c>
+      <c r="D23" s="10">
+        <v>44089</v>
+      </c>
+      <c r="E23" s="1">
+        <v>270</v>
+      </c>
+      <c r="F23" s="1">
+        <v>4092289</v>
+      </c>
+      <c r="G23" s="1">
+        <v>4015701</v>
+      </c>
+      <c r="H23" s="1">
+        <v>4188540</v>
+      </c>
+      <c r="I23" s="1">
+        <v>4188539</v>
+      </c>
+    </row>
+    <row r="24" spans="1:10" ht="16" x14ac:dyDescent="0.2">
+      <c r="A24" s="1">
+        <v>105</v>
+      </c>
+      <c r="B24" s="1">
+        <v>45</v>
+      </c>
+      <c r="C24" s="10">
+        <v>43845</v>
+      </c>
+      <c r="D24" s="10">
+        <v>44101</v>
+      </c>
+      <c r="E24" s="1">
+        <v>270</v>
+      </c>
+      <c r="F24" s="1">
+        <v>4092289</v>
+      </c>
+      <c r="G24" s="1">
+        <v>4015701</v>
+      </c>
+      <c r="H24" s="1">
+        <v>4188540</v>
+      </c>
+      <c r="I24" s="1">
+        <v>4188539</v>
+      </c>
+    </row>
+    <row r="25" spans="1:10" ht="16" x14ac:dyDescent="0.2">
+      <c r="A25" s="1">
+        <v>106</v>
+      </c>
+      <c r="B25" s="1">
+        <v>46</v>
+      </c>
+      <c r="C25" s="10">
+        <v>43832</v>
+      </c>
+      <c r="D25" s="10">
+        <v>44089</v>
+      </c>
+      <c r="E25" s="1">
+        <v>270</v>
+      </c>
+      <c r="F25" s="1">
+        <v>4092289</v>
+      </c>
+      <c r="G25" s="1">
+        <v>4015701</v>
+      </c>
+      <c r="H25" s="1">
+        <v>4188540</v>
+      </c>
+      <c r="I25" s="1">
+        <v>4188539</v>
+      </c>
+    </row>
+    <row r="26" spans="1:10" ht="16" x14ac:dyDescent="0.2">
+      <c r="A26" s="1">
+        <v>106</v>
+      </c>
+      <c r="B26" s="1">
+        <v>46</v>
+      </c>
+      <c r="C26" s="10">
+        <v>42005</v>
+      </c>
+      <c r="D26" s="10">
+        <v>42248</v>
+      </c>
+      <c r="E26" s="1">
+        <v>270</v>
+      </c>
+      <c r="F26" s="1">
+        <v>4092289</v>
+      </c>
+      <c r="G26" s="1">
+        <v>4015701</v>
+      </c>
+      <c r="H26" s="1">
+        <v>4188540</v>
+      </c>
+      <c r="I26" s="1">
+        <v>4188539</v>
+      </c>
+    </row>
   </sheetData>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:I17">
     <sortCondition ref="G1:G17"/>
@@ -1865,7 +2040,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E2B8B433-8712-6348-9439-118BA945D9FC}">
-  <dimension ref="A1:E25"/>
+  <dimension ref="A1:E27"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11.5" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="22.1640625" bestFit="1" customWidth="1"/>
@@ -2296,6 +2471,40 @@
         <v>45657</v>
       </c>
       <c r="E25" s="1">
+        <v>32880</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5" ht="16" x14ac:dyDescent="0.2">
+      <c r="A26" s="1">
+        <v>105</v>
+      </c>
+      <c r="B26" s="1">
+        <v>105</v>
+      </c>
+      <c r="C26" s="6">
+        <v>38718</v>
+      </c>
+      <c r="D26" s="6">
+        <v>45657</v>
+      </c>
+      <c r="E26" s="1">
+        <v>32880</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5" ht="16" x14ac:dyDescent="0.2">
+      <c r="A27" s="1">
+        <v>106</v>
+      </c>
+      <c r="B27" s="1">
+        <v>106</v>
+      </c>
+      <c r="C27" s="6">
+        <v>38718</v>
+      </c>
+      <c r="D27" s="6">
+        <v>45657</v>
+      </c>
+      <c r="E27" s="1">
         <v>32880</v>
       </c>
     </row>
@@ -4028,6 +4237,25 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="2f696df8-7461-455e-9bf1-ef56149775f2">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101005E48E57FAF33F44FB5E762D78C70B43B" ma:contentTypeVersion="9" ma:contentTypeDescription="Een nieuw document maken." ma:contentTypeScope="" ma:versionID="09261b8c9db6496040fa98c128102db7">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="2f696df8-7461-455e-9bf1-ef56149775f2" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="c87049393a058ff896145aa7aaeb09f0" ns2:_="">
     <xsd:import namespace="2f696df8-7461-455e-9bf1-ef56149775f2"/>
@@ -4199,39 +4427,10 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="2f696df8-7461-455e-9bf1-ef56149775f2">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5C331738-2870-4EAF-86B4-6F4811A40645}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{24F405B8-D94E-404D-BACC-4EAF448A1B08}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="2f696df8-7461-455e-9bf1-ef56149775f2"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -4253,9 +4452,19 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{24F405B8-D94E-404D-BACC-4EAF448A1B08}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5C331738-2870-4EAF-86B4-6F4811A40645}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="2f696df8-7461-455e-9bf1-ef56149775f2"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
--- a/tests/testthat/testCases/Test_data_sansComments.xlsx
+++ b/tests/testthat/testCases/Test_data_sansComments.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/aalamshahi/Packages/PETConnector/tests/testthat/testCases/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{59E8A64A-B2C6-F949-B5CD-B22724A044A3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D879A57B-EB7B-7040-A660-71E854ADEE90}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="6220" yWindow="2020" windowWidth="25600" windowHeight="15500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="17340" yWindow="920" windowWidth="17060" windowHeight="19920" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="person" sheetId="1" r:id="rId1"/>
@@ -1252,7 +1252,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BB104438-4099-6E40-90B1-739F61573A13}">
-  <dimension ref="A1:J26"/>
+  <dimension ref="A1:J27"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11.5" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="2" max="2" width="18.6640625" customWidth="1"/>
@@ -1855,6 +1855,7 @@
       <c r="I20" s="1">
         <v>4188539</v>
       </c>
+      <c r="J20" s="1"/>
     </row>
     <row r="21" spans="1:10" ht="16" x14ac:dyDescent="0.2">
       <c r="A21" s="1">
@@ -1884,8 +1885,9 @@
       <c r="I21" s="1">
         <v>4188539</v>
       </c>
-    </row>
-    <row r="22" spans="1:10" ht="16" x14ac:dyDescent="0.2">
+      <c r="J21" s="1"/>
+    </row>
+    <row r="22" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A22" s="1">
         <v>105</v>
       </c>
@@ -1913,6 +1915,7 @@
       <c r="I22" s="1">
         <v>4188539</v>
       </c>
+      <c r="J22" s="1"/>
     </row>
     <row r="23" spans="1:10" ht="16" x14ac:dyDescent="0.2">
       <c r="A23" s="1">
@@ -1942,6 +1945,7 @@
       <c r="I23" s="1">
         <v>4188539</v>
       </c>
+      <c r="J23" s="1"/>
     </row>
     <row r="24" spans="1:10" ht="16" x14ac:dyDescent="0.2">
       <c r="A24" s="1">
@@ -1951,10 +1955,10 @@
         <v>45</v>
       </c>
       <c r="C24" s="10">
-        <v>43845</v>
+        <v>43832</v>
       </c>
       <c r="D24" s="10">
-        <v>44101</v>
+        <v>44090</v>
       </c>
       <c r="E24" s="1">
         <v>270</v>
@@ -1971,19 +1975,20 @@
       <c r="I24" s="1">
         <v>4188539</v>
       </c>
+      <c r="J24" s="1"/>
     </row>
     <row r="25" spans="1:10" ht="16" x14ac:dyDescent="0.2">
       <c r="A25" s="1">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="B25" s="1">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C25" s="10">
-        <v>43832</v>
+        <v>43845</v>
       </c>
       <c r="D25" s="10">
-        <v>44089</v>
+        <v>44101</v>
       </c>
       <c r="E25" s="1">
         <v>270</v>
@@ -2000,6 +2005,7 @@
       <c r="I25" s="1">
         <v>4188539</v>
       </c>
+      <c r="J25" s="1"/>
     </row>
     <row r="26" spans="1:10" ht="16" x14ac:dyDescent="0.2">
       <c r="A26" s="1">
@@ -2009,10 +2015,10 @@
         <v>46</v>
       </c>
       <c r="C26" s="10">
-        <v>42005</v>
+        <v>43832</v>
       </c>
       <c r="D26" s="10">
-        <v>42248</v>
+        <v>44089</v>
       </c>
       <c r="E26" s="1">
         <v>270</v>
@@ -2029,6 +2035,37 @@
       <c r="I26" s="1">
         <v>4188539</v>
       </c>
+      <c r="J26" s="1"/>
+    </row>
+    <row r="27" spans="1:10" ht="16" x14ac:dyDescent="0.2">
+      <c r="A27" s="1">
+        <v>106</v>
+      </c>
+      <c r="B27" s="1">
+        <v>46</v>
+      </c>
+      <c r="C27" s="10">
+        <v>42005</v>
+      </c>
+      <c r="D27" s="10">
+        <v>42248</v>
+      </c>
+      <c r="E27" s="1">
+        <v>270</v>
+      </c>
+      <c r="F27" s="1">
+        <v>4092289</v>
+      </c>
+      <c r="G27" s="1">
+        <v>4015701</v>
+      </c>
+      <c r="H27" s="1">
+        <v>4188540</v>
+      </c>
+      <c r="I27" s="1">
+        <v>4188539</v>
+      </c>
+      <c r="J27" s="1"/>
     </row>
   </sheetData>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:I17">
@@ -4237,25 +4274,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="2f696df8-7461-455e-9bf1-ef56149775f2">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101005E48E57FAF33F44FB5E762D78C70B43B" ma:contentTypeVersion="9" ma:contentTypeDescription="Een nieuw document maken." ma:contentTypeScope="" ma:versionID="09261b8c9db6496040fa98c128102db7">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="2f696df8-7461-455e-9bf1-ef56149775f2" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="c87049393a058ff896145aa7aaeb09f0" ns2:_="">
     <xsd:import namespace="2f696df8-7461-455e-9bf1-ef56149775f2"/>
@@ -4427,10 +4445,39 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="2f696df8-7461-455e-9bf1-ef56149775f2">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{24F405B8-D94E-404D-BACC-4EAF448A1B08}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5C331738-2870-4EAF-86B4-6F4811A40645}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="2f696df8-7461-455e-9bf1-ef56149775f2"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -4452,19 +4499,9 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5C331738-2870-4EAF-86B4-6F4811A40645}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{24F405B8-D94E-404D-BACC-4EAF448A1B08}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="2f696df8-7461-455e-9bf1-ef56149775f2"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>